--- a/Marketing_Campaign_ROI_v2.xlsx
+++ b/Marketing_Campaign_ROI_v2.xlsx
@@ -3668,7 +3668,7 @@
     <row r="2" ht="15" customHeight="1" s="66">
       <c r="A2" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025001</t>
+          <t>CAMP-2026001</t>
         </is>
       </c>
       <c r="B2" s="94" t="inlineStr">
@@ -3758,7 +3758,7 @@
     <row r="3" ht="15" customHeight="1" s="66">
       <c r="A3" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025002</t>
+          <t>CAMP-2026002</t>
         </is>
       </c>
       <c r="B3" s="102" t="inlineStr">
@@ -3848,7 +3848,7 @@
     <row r="4" ht="15" customHeight="1" s="66">
       <c r="A4" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025003</t>
+          <t>CAMP-2026003</t>
         </is>
       </c>
       <c r="B4" s="94" t="inlineStr">
@@ -3938,7 +3938,7 @@
     <row r="5" ht="15" customHeight="1" s="66">
       <c r="A5" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025004</t>
+          <t>CAMP-2026004</t>
         </is>
       </c>
       <c r="B5" s="102" t="inlineStr">
@@ -4028,7 +4028,7 @@
     <row r="6" ht="15" customHeight="1" s="66">
       <c r="A6" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025005</t>
+          <t>CAMP-2026005</t>
         </is>
       </c>
       <c r="B6" s="94" t="inlineStr">
@@ -4118,7 +4118,7 @@
     <row r="7" ht="15" customHeight="1" s="66">
       <c r="A7" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025006</t>
+          <t>CAMP-2026006</t>
         </is>
       </c>
       <c r="B7" s="102" t="inlineStr">
@@ -4208,7 +4208,7 @@
     <row r="8" ht="15" customHeight="1" s="66">
       <c r="A8" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025007</t>
+          <t>CAMP-2026007</t>
         </is>
       </c>
       <c r="B8" s="94" t="inlineStr">
@@ -4298,7 +4298,7 @@
     <row r="9" ht="15" customHeight="1" s="66">
       <c r="A9" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025008</t>
+          <t>CAMP-2026008</t>
         </is>
       </c>
       <c r="B9" s="102" t="inlineStr">
@@ -4388,7 +4388,7 @@
     <row r="10" ht="15" customHeight="1" s="66">
       <c r="A10" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025009</t>
+          <t>CAMP-2026009</t>
         </is>
       </c>
       <c r="B10" s="94" t="inlineStr">
@@ -4478,7 +4478,7 @@
     <row r="11" ht="15" customHeight="1" s="66">
       <c r="A11" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025010</t>
+          <t>CAMP-2026010</t>
         </is>
       </c>
       <c r="B11" s="102" t="inlineStr">
@@ -4568,7 +4568,7 @@
     <row r="12" ht="15" customHeight="1" s="66">
       <c r="A12" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025011</t>
+          <t>CAMP-2026011</t>
         </is>
       </c>
       <c r="B12" s="94" t="inlineStr">
@@ -4658,7 +4658,7 @@
     <row r="13" ht="15" customHeight="1" s="66">
       <c r="A13" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025012</t>
+          <t>CAMP-2026012</t>
         </is>
       </c>
       <c r="B13" s="102" t="inlineStr">
@@ -4748,7 +4748,7 @@
     <row r="14" ht="15" customHeight="1" s="66">
       <c r="A14" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025013</t>
+          <t>CAMP-2026013</t>
         </is>
       </c>
       <c r="B14" s="94" t="inlineStr">
@@ -4838,7 +4838,7 @@
     <row r="15" ht="15" customHeight="1" s="66">
       <c r="A15" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025014</t>
+          <t>CAMP-2026014</t>
         </is>
       </c>
       <c r="B15" s="102" t="inlineStr">
@@ -4928,7 +4928,7 @@
     <row r="16" ht="15" customHeight="1" s="66">
       <c r="A16" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025015</t>
+          <t>CAMP-2026015</t>
         </is>
       </c>
       <c r="B16" s="94" t="inlineStr">
@@ -5018,7 +5018,7 @@
     <row r="17" ht="15" customHeight="1" s="66">
       <c r="A17" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025016</t>
+          <t>CAMP-2026016</t>
         </is>
       </c>
       <c r="B17" s="102" t="inlineStr">
@@ -5108,7 +5108,7 @@
     <row r="18" ht="15" customHeight="1" s="66">
       <c r="A18" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025017</t>
+          <t>CAMP-2026017</t>
         </is>
       </c>
       <c r="B18" s="94" t="inlineStr">
@@ -5198,7 +5198,7 @@
     <row r="19" ht="15" customHeight="1" s="66">
       <c r="A19" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025018</t>
+          <t>CAMP-2026018</t>
         </is>
       </c>
       <c r="B19" s="102" t="inlineStr">
@@ -5288,7 +5288,7 @@
     <row r="20" ht="15" customHeight="1" s="66">
       <c r="A20" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025019</t>
+          <t>CAMP-2026019</t>
         </is>
       </c>
       <c r="B20" s="94" t="inlineStr">
@@ -5378,7 +5378,7 @@
     <row r="21" ht="15" customHeight="1" s="66">
       <c r="A21" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025020</t>
+          <t>CAMP-2026020</t>
         </is>
       </c>
       <c r="B21" s="102" t="inlineStr">
@@ -5468,7 +5468,7 @@
     <row r="22" ht="15" customHeight="1" s="66">
       <c r="A22" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025021</t>
+          <t>CAMP-2026021</t>
         </is>
       </c>
       <c r="B22" s="94" t="inlineStr">
@@ -5558,7 +5558,7 @@
     <row r="23" ht="15" customHeight="1" s="66">
       <c r="A23" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025022</t>
+          <t>CAMP-2026022</t>
         </is>
       </c>
       <c r="B23" s="102" t="inlineStr">
@@ -5648,7 +5648,7 @@
     <row r="24" ht="15" customHeight="1" s="66">
       <c r="A24" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025023</t>
+          <t>CAMP-2026023</t>
         </is>
       </c>
       <c r="B24" s="94" t="inlineStr">
@@ -5738,7 +5738,7 @@
     <row r="25" ht="15" customHeight="1" s="66">
       <c r="A25" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025024</t>
+          <t>CAMP-2026024</t>
         </is>
       </c>
       <c r="B25" s="102" t="inlineStr">
@@ -5828,7 +5828,7 @@
     <row r="26" ht="15" customHeight="1" s="66">
       <c r="A26" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025025</t>
+          <t>CAMP-2026025</t>
         </is>
       </c>
       <c r="B26" s="94" t="inlineStr">
@@ -5918,7 +5918,7 @@
     <row r="27" ht="15" customHeight="1" s="66">
       <c r="A27" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025026</t>
+          <t>CAMP-2026026</t>
         </is>
       </c>
       <c r="B27" s="102" t="inlineStr">
@@ -6008,7 +6008,7 @@
     <row r="28" ht="15" customHeight="1" s="66">
       <c r="A28" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025027</t>
+          <t>CAMP-2026027</t>
         </is>
       </c>
       <c r="B28" s="94" t="inlineStr">
@@ -6098,7 +6098,7 @@
     <row r="29" ht="15" customHeight="1" s="66">
       <c r="A29" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025028</t>
+          <t>CAMP-2026028</t>
         </is>
       </c>
       <c r="B29" s="102" t="inlineStr">
@@ -6188,7 +6188,7 @@
     <row r="30" ht="15" customHeight="1" s="66">
       <c r="A30" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025029</t>
+          <t>CAMP-2026029</t>
         </is>
       </c>
       <c r="B30" s="94" t="inlineStr">
@@ -6278,7 +6278,7 @@
     <row r="31" ht="15" customHeight="1" s="66">
       <c r="A31" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025030</t>
+          <t>CAMP-2026030</t>
         </is>
       </c>
       <c r="B31" s="102" t="inlineStr">
@@ -6368,7 +6368,7 @@
     <row r="32" ht="15" customHeight="1" s="66">
       <c r="A32" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025031</t>
+          <t>CAMP-2026031</t>
         </is>
       </c>
       <c r="B32" s="94" t="inlineStr">
@@ -6458,7 +6458,7 @@
     <row r="33" ht="15" customHeight="1" s="66">
       <c r="A33" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025032</t>
+          <t>CAMP-2026032</t>
         </is>
       </c>
       <c r="B33" s="102" t="inlineStr">
@@ -6548,7 +6548,7 @@
     <row r="34" ht="15" customHeight="1" s="66">
       <c r="A34" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025033</t>
+          <t>CAMP-2026033</t>
         </is>
       </c>
       <c r="B34" s="94" t="inlineStr">
@@ -6638,7 +6638,7 @@
     <row r="35" ht="15" customHeight="1" s="66">
       <c r="A35" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025034</t>
+          <t>CAMP-2026034</t>
         </is>
       </c>
       <c r="B35" s="102" t="inlineStr">
@@ -6728,7 +6728,7 @@
     <row r="36" ht="15" customHeight="1" s="66">
       <c r="A36" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025035</t>
+          <t>CAMP-2026035</t>
         </is>
       </c>
       <c r="B36" s="94" t="inlineStr">
@@ -6818,7 +6818,7 @@
     <row r="37" ht="15" customHeight="1" s="66">
       <c r="A37" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025036</t>
+          <t>CAMP-2026036</t>
         </is>
       </c>
       <c r="B37" s="102" t="inlineStr">
@@ -6908,7 +6908,7 @@
     <row r="38" ht="15" customHeight="1" s="66">
       <c r="A38" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025037</t>
+          <t>CAMP-2026037</t>
         </is>
       </c>
       <c r="B38" s="94" t="inlineStr">
@@ -6998,7 +6998,7 @@
     <row r="39" ht="15" customHeight="1" s="66">
       <c r="A39" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025038</t>
+          <t>CAMP-2026038</t>
         </is>
       </c>
       <c r="B39" s="102" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="40" ht="15" customHeight="1" s="66">
       <c r="A40" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025039</t>
+          <t>CAMP-2026039</t>
         </is>
       </c>
       <c r="B40" s="94" t="inlineStr">
@@ -7178,7 +7178,7 @@
     <row r="41" ht="15" customHeight="1" s="66">
       <c r="A41" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025040</t>
+          <t>CAMP-2026040</t>
         </is>
       </c>
       <c r="B41" s="102" t="inlineStr">
@@ -7268,7 +7268,7 @@
     <row r="42" ht="15" customHeight="1" s="66">
       <c r="A42" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025041</t>
+          <t>CAMP-2026041</t>
         </is>
       </c>
       <c r="B42" s="94" t="inlineStr">
@@ -7358,7 +7358,7 @@
     <row r="43" ht="15" customHeight="1" s="66">
       <c r="A43" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025042</t>
+          <t>CAMP-2026042</t>
         </is>
       </c>
       <c r="B43" s="102" t="inlineStr">
@@ -7448,7 +7448,7 @@
     <row r="44" ht="15" customHeight="1" s="66">
       <c r="A44" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025043</t>
+          <t>CAMP-2026043</t>
         </is>
       </c>
       <c r="B44" s="94" t="inlineStr">
@@ -7538,7 +7538,7 @@
     <row r="45" ht="15" customHeight="1" s="66">
       <c r="A45" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025044</t>
+          <t>CAMP-2026044</t>
         </is>
       </c>
       <c r="B45" s="102" t="inlineStr">
@@ -7628,7 +7628,7 @@
     <row r="46" ht="15" customHeight="1" s="66">
       <c r="A46" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025045</t>
+          <t>CAMP-2026045</t>
         </is>
       </c>
       <c r="B46" s="94" t="inlineStr">
@@ -7718,7 +7718,7 @@
     <row r="47" ht="15" customHeight="1" s="66">
       <c r="A47" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025046</t>
+          <t>CAMP-2026046</t>
         </is>
       </c>
       <c r="B47" s="102" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="48" ht="15" customHeight="1" s="66">
       <c r="A48" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025047</t>
+          <t>CAMP-2026047</t>
         </is>
       </c>
       <c r="B48" s="94" t="inlineStr">
@@ -7898,7 +7898,7 @@
     <row r="49" ht="15" customHeight="1" s="66">
       <c r="A49" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025048</t>
+          <t>CAMP-2026048</t>
         </is>
       </c>
       <c r="B49" s="102" t="inlineStr">
@@ -7988,7 +7988,7 @@
     <row r="50" ht="15" customHeight="1" s="66">
       <c r="A50" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025049</t>
+          <t>CAMP-2026049</t>
         </is>
       </c>
       <c r="B50" s="94" t="inlineStr">
@@ -8078,7 +8078,7 @@
     <row r="51" ht="15" customHeight="1" s="66">
       <c r="A51" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025050</t>
+          <t>CAMP-2026050</t>
         </is>
       </c>
       <c r="B51" s="102" t="inlineStr">
@@ -8168,7 +8168,7 @@
     <row r="52" ht="15" customHeight="1" s="66">
       <c r="A52" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025051</t>
+          <t>CAMP-2026051</t>
         </is>
       </c>
       <c r="B52" s="94" t="inlineStr">
@@ -8258,7 +8258,7 @@
     <row r="53" ht="15" customHeight="1" s="66">
       <c r="A53" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025052</t>
+          <t>CAMP-2026052</t>
         </is>
       </c>
       <c r="B53" s="102" t="inlineStr">
@@ -8348,7 +8348,7 @@
     <row r="54" ht="15" customHeight="1" s="66">
       <c r="A54" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025053</t>
+          <t>CAMP-2026053</t>
         </is>
       </c>
       <c r="B54" s="94" t="inlineStr">
@@ -8438,7 +8438,7 @@
     <row r="55" ht="15" customHeight="1" s="66">
       <c r="A55" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025054</t>
+          <t>CAMP-2026054</t>
         </is>
       </c>
       <c r="B55" s="102" t="inlineStr">
@@ -8528,7 +8528,7 @@
     <row r="56" ht="15" customHeight="1" s="66">
       <c r="A56" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025055</t>
+          <t>CAMP-2026055</t>
         </is>
       </c>
       <c r="B56" s="94" t="inlineStr">
@@ -8618,7 +8618,7 @@
     <row r="57" ht="15" customHeight="1" s="66">
       <c r="A57" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025056</t>
+          <t>CAMP-2026056</t>
         </is>
       </c>
       <c r="B57" s="102" t="inlineStr">
@@ -8708,7 +8708,7 @@
     <row r="58" ht="15" customHeight="1" s="66">
       <c r="A58" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025057</t>
+          <t>CAMP-2026057</t>
         </is>
       </c>
       <c r="B58" s="94" t="inlineStr">
@@ -8798,7 +8798,7 @@
     <row r="59" ht="15" customHeight="1" s="66">
       <c r="A59" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025058</t>
+          <t>CAMP-2026058</t>
         </is>
       </c>
       <c r="B59" s="102" t="inlineStr">
@@ -8888,7 +8888,7 @@
     <row r="60" ht="15" customHeight="1" s="66">
       <c r="A60" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025059</t>
+          <t>CAMP-2026059</t>
         </is>
       </c>
       <c r="B60" s="94" t="inlineStr">
@@ -8978,7 +8978,7 @@
     <row r="61" ht="15" customHeight="1" s="66">
       <c r="A61" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025060</t>
+          <t>CAMP-2026060</t>
         </is>
       </c>
       <c r="B61" s="102" t="inlineStr">
@@ -9068,7 +9068,7 @@
     <row r="62" ht="15" customHeight="1" s="66">
       <c r="A62" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025061</t>
+          <t>CAMP-2026061</t>
         </is>
       </c>
       <c r="B62" s="94" t="inlineStr">
@@ -9158,7 +9158,7 @@
     <row r="63" ht="15" customHeight="1" s="66">
       <c r="A63" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025062</t>
+          <t>CAMP-2026062</t>
         </is>
       </c>
       <c r="B63" s="102" t="inlineStr">
@@ -9248,7 +9248,7 @@
     <row r="64" ht="15" customHeight="1" s="66">
       <c r="A64" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025063</t>
+          <t>CAMP-2026063</t>
         </is>
       </c>
       <c r="B64" s="94" t="inlineStr">
@@ -9338,7 +9338,7 @@
     <row r="65" ht="15" customHeight="1" s="66">
       <c r="A65" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025064</t>
+          <t>CAMP-2026064</t>
         </is>
       </c>
       <c r="B65" s="102" t="inlineStr">
@@ -9428,7 +9428,7 @@
     <row r="66" ht="15" customHeight="1" s="66">
       <c r="A66" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025065</t>
+          <t>CAMP-2026065</t>
         </is>
       </c>
       <c r="B66" s="94" t="inlineStr">
@@ -9518,7 +9518,7 @@
     <row r="67" ht="15" customHeight="1" s="66">
       <c r="A67" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025066</t>
+          <t>CAMP-2026066</t>
         </is>
       </c>
       <c r="B67" s="102" t="inlineStr">
@@ -9608,7 +9608,7 @@
     <row r="68" ht="15" customHeight="1" s="66">
       <c r="A68" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025067</t>
+          <t>CAMP-2026067</t>
         </is>
       </c>
       <c r="B68" s="94" t="inlineStr">
@@ -9698,7 +9698,7 @@
     <row r="69" ht="15" customHeight="1" s="66">
       <c r="A69" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025068</t>
+          <t>CAMP-2026068</t>
         </is>
       </c>
       <c r="B69" s="102" t="inlineStr">
@@ -9788,7 +9788,7 @@
     <row r="70" ht="15" customHeight="1" s="66">
       <c r="A70" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025069</t>
+          <t>CAMP-2026069</t>
         </is>
       </c>
       <c r="B70" s="94" t="inlineStr">
@@ -9878,7 +9878,7 @@
     <row r="71" ht="15" customHeight="1" s="66">
       <c r="A71" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025070</t>
+          <t>CAMP-2026070</t>
         </is>
       </c>
       <c r="B71" s="102" t="inlineStr">
@@ -9968,7 +9968,7 @@
     <row r="72" ht="15" customHeight="1" s="66">
       <c r="A72" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025071</t>
+          <t>CAMP-2026071</t>
         </is>
       </c>
       <c r="B72" s="94" t="inlineStr">
@@ -10058,7 +10058,7 @@
     <row r="73" ht="15" customHeight="1" s="66">
       <c r="A73" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025072</t>
+          <t>CAMP-2026072</t>
         </is>
       </c>
       <c r="B73" s="102" t="inlineStr">
@@ -10148,7 +10148,7 @@
     <row r="74" ht="15" customHeight="1" s="66">
       <c r="A74" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025073</t>
+          <t>CAMP-2026073</t>
         </is>
       </c>
       <c r="B74" s="94" t="inlineStr">
@@ -10238,7 +10238,7 @@
     <row r="75" ht="15" customHeight="1" s="66">
       <c r="A75" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025074</t>
+          <t>CAMP-2026074</t>
         </is>
       </c>
       <c r="B75" s="102" t="inlineStr">
@@ -10328,7 +10328,7 @@
     <row r="76" ht="15" customHeight="1" s="66">
       <c r="A76" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025075</t>
+          <t>CAMP-2026075</t>
         </is>
       </c>
       <c r="B76" s="94" t="inlineStr">
@@ -10418,7 +10418,7 @@
     <row r="77" ht="15" customHeight="1" s="66">
       <c r="A77" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025076</t>
+          <t>CAMP-2026076</t>
         </is>
       </c>
       <c r="B77" s="102" t="inlineStr">
@@ -10508,7 +10508,7 @@
     <row r="78" ht="15" customHeight="1" s="66">
       <c r="A78" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025077</t>
+          <t>CAMP-2026077</t>
         </is>
       </c>
       <c r="B78" s="94" t="inlineStr">
@@ -10598,7 +10598,7 @@
     <row r="79" ht="15" customHeight="1" s="66">
       <c r="A79" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025078</t>
+          <t>CAMP-2026078</t>
         </is>
       </c>
       <c r="B79" s="102" t="inlineStr">
@@ -10688,7 +10688,7 @@
     <row r="80" ht="15" customHeight="1" s="66">
       <c r="A80" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025079</t>
+          <t>CAMP-2026079</t>
         </is>
       </c>
       <c r="B80" s="94" t="inlineStr">
@@ -10778,7 +10778,7 @@
     <row r="81" ht="15" customHeight="1" s="66">
       <c r="A81" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025080</t>
+          <t>CAMP-2026080</t>
         </is>
       </c>
       <c r="B81" s="102" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="82" ht="15" customHeight="1" s="66">
       <c r="A82" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025081</t>
+          <t>CAMP-2026081</t>
         </is>
       </c>
       <c r="B82" s="94" t="inlineStr">
@@ -10958,7 +10958,7 @@
     <row r="83" ht="15" customHeight="1" s="66">
       <c r="A83" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025082</t>
+          <t>CAMP-2026082</t>
         </is>
       </c>
       <c r="B83" s="102" t="inlineStr">
@@ -11048,7 +11048,7 @@
     <row r="84" ht="15" customHeight="1" s="66">
       <c r="A84" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025083</t>
+          <t>CAMP-2026083</t>
         </is>
       </c>
       <c r="B84" s="94" t="inlineStr">
@@ -11138,7 +11138,7 @@
     <row r="85" ht="15" customHeight="1" s="66">
       <c r="A85" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025084</t>
+          <t>CAMP-2026084</t>
         </is>
       </c>
       <c r="B85" s="102" t="inlineStr">
@@ -11228,7 +11228,7 @@
     <row r="86" ht="15" customHeight="1" s="66">
       <c r="A86" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025085</t>
+          <t>CAMP-2026085</t>
         </is>
       </c>
       <c r="B86" s="94" t="inlineStr">
@@ -11318,7 +11318,7 @@
     <row r="87" ht="15" customHeight="1" s="66">
       <c r="A87" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025086</t>
+          <t>CAMP-2026086</t>
         </is>
       </c>
       <c r="B87" s="102" t="inlineStr">
@@ -11408,7 +11408,7 @@
     <row r="88" ht="15" customHeight="1" s="66">
       <c r="A88" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025087</t>
+          <t>CAMP-2026087</t>
         </is>
       </c>
       <c r="B88" s="94" t="inlineStr">
@@ -11498,7 +11498,7 @@
     <row r="89" ht="15" customHeight="1" s="66">
       <c r="A89" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025088</t>
+          <t>CAMP-2026088</t>
         </is>
       </c>
       <c r="B89" s="102" t="inlineStr">
@@ -11588,7 +11588,7 @@
     <row r="90" ht="15" customHeight="1" s="66">
       <c r="A90" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025089</t>
+          <t>CAMP-2026089</t>
         </is>
       </c>
       <c r="B90" s="94" t="inlineStr">
@@ -11678,7 +11678,7 @@
     <row r="91" ht="15" customHeight="1" s="66">
       <c r="A91" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025090</t>
+          <t>CAMP-2026090</t>
         </is>
       </c>
       <c r="B91" s="102" t="inlineStr">
@@ -11768,7 +11768,7 @@
     <row r="92" ht="15" customHeight="1" s="66">
       <c r="A92" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025091</t>
+          <t>CAMP-2026091</t>
         </is>
       </c>
       <c r="B92" s="94" t="inlineStr">
@@ -11858,7 +11858,7 @@
     <row r="93" ht="15" customHeight="1" s="66">
       <c r="A93" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025092</t>
+          <t>CAMP-2026092</t>
         </is>
       </c>
       <c r="B93" s="102" t="inlineStr">
@@ -11948,7 +11948,7 @@
     <row r="94" ht="15" customHeight="1" s="66">
       <c r="A94" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025093</t>
+          <t>CAMP-2026093</t>
         </is>
       </c>
       <c r="B94" s="94" t="inlineStr">
@@ -12038,7 +12038,7 @@
     <row r="95" ht="15" customHeight="1" s="66">
       <c r="A95" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025094</t>
+          <t>CAMP-2026094</t>
         </is>
       </c>
       <c r="B95" s="102" t="inlineStr">
@@ -12128,7 +12128,7 @@
     <row r="96" ht="15" customHeight="1" s="66">
       <c r="A96" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025095</t>
+          <t>CAMP-2026095</t>
         </is>
       </c>
       <c r="B96" s="94" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="97" ht="15" customHeight="1" s="66">
       <c r="A97" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025096</t>
+          <t>CAMP-2026096</t>
         </is>
       </c>
       <c r="B97" s="102" t="inlineStr">
@@ -12308,7 +12308,7 @@
     <row r="98" ht="15" customHeight="1" s="66">
       <c r="A98" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025097</t>
+          <t>CAMP-2026097</t>
         </is>
       </c>
       <c r="B98" s="94" t="inlineStr">
@@ -12398,7 +12398,7 @@
     <row r="99" ht="15" customHeight="1" s="66">
       <c r="A99" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025098</t>
+          <t>CAMP-2026098</t>
         </is>
       </c>
       <c r="B99" s="102" t="inlineStr">
@@ -12488,7 +12488,7 @@
     <row r="100" ht="15" customHeight="1" s="66">
       <c r="A100" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025099</t>
+          <t>CAMP-2026099</t>
         </is>
       </c>
       <c r="B100" s="94" t="inlineStr">
@@ -12578,7 +12578,7 @@
     <row r="101" ht="15" customHeight="1" s="66">
       <c r="A101" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025100</t>
+          <t>CAMP-2026100</t>
         </is>
       </c>
       <c r="B101" s="102" t="inlineStr">
@@ -12668,7 +12668,7 @@
     <row r="102" ht="15" customHeight="1" s="66">
       <c r="A102" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025101</t>
+          <t>CAMP-2026101</t>
         </is>
       </c>
       <c r="B102" s="94" t="inlineStr">
@@ -12758,7 +12758,7 @@
     <row r="103" ht="15" customHeight="1" s="66">
       <c r="A103" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025102</t>
+          <t>CAMP-2026102</t>
         </is>
       </c>
       <c r="B103" s="102" t="inlineStr">
@@ -12848,7 +12848,7 @@
     <row r="104" ht="15" customHeight="1" s="66">
       <c r="A104" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025103</t>
+          <t>CAMP-2026103</t>
         </is>
       </c>
       <c r="B104" s="94" t="inlineStr">
@@ -12938,7 +12938,7 @@
     <row r="105" ht="15" customHeight="1" s="66">
       <c r="A105" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025104</t>
+          <t>CAMP-2026104</t>
         </is>
       </c>
       <c r="B105" s="102" t="inlineStr">
@@ -13028,7 +13028,7 @@
     <row r="106" ht="15" customHeight="1" s="66">
       <c r="A106" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025105</t>
+          <t>CAMP-2026105</t>
         </is>
       </c>
       <c r="B106" s="94" t="inlineStr">
@@ -13118,7 +13118,7 @@
     <row r="107" ht="15" customHeight="1" s="66">
       <c r="A107" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025106</t>
+          <t>CAMP-2026106</t>
         </is>
       </c>
       <c r="B107" s="102" t="inlineStr">
@@ -13208,7 +13208,7 @@
     <row r="108" ht="15" customHeight="1" s="66">
       <c r="A108" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025107</t>
+          <t>CAMP-2026107</t>
         </is>
       </c>
       <c r="B108" s="94" t="inlineStr">
@@ -13298,7 +13298,7 @@
     <row r="109" ht="15" customHeight="1" s="66">
       <c r="A109" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025108</t>
+          <t>CAMP-2026108</t>
         </is>
       </c>
       <c r="B109" s="102" t="inlineStr">
@@ -13388,7 +13388,7 @@
     <row r="110" ht="15" customHeight="1" s="66">
       <c r="A110" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025109</t>
+          <t>CAMP-2026109</t>
         </is>
       </c>
       <c r="B110" s="94" t="inlineStr">
@@ -13478,7 +13478,7 @@
     <row r="111" ht="15" customHeight="1" s="66">
       <c r="A111" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025110</t>
+          <t>CAMP-2026110</t>
         </is>
       </c>
       <c r="B111" s="102" t="inlineStr">
@@ -13568,7 +13568,7 @@
     <row r="112" ht="15" customHeight="1" s="66">
       <c r="A112" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025111</t>
+          <t>CAMP-2026111</t>
         </is>
       </c>
       <c r="B112" s="94" t="inlineStr">
@@ -13658,7 +13658,7 @@
     <row r="113" ht="15" customHeight="1" s="66">
       <c r="A113" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025112</t>
+          <t>CAMP-2026112</t>
         </is>
       </c>
       <c r="B113" s="102" t="inlineStr">
@@ -13748,7 +13748,7 @@
     <row r="114" ht="15" customHeight="1" s="66">
       <c r="A114" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025113</t>
+          <t>CAMP-2026113</t>
         </is>
       </c>
       <c r="B114" s="94" t="inlineStr">
@@ -13838,7 +13838,7 @@
     <row r="115" ht="15" customHeight="1" s="66">
       <c r="A115" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025114</t>
+          <t>CAMP-2026114</t>
         </is>
       </c>
       <c r="B115" s="102" t="inlineStr">
@@ -13928,7 +13928,7 @@
     <row r="116" ht="15" customHeight="1" s="66">
       <c r="A116" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025115</t>
+          <t>CAMP-2026115</t>
         </is>
       </c>
       <c r="B116" s="94" t="inlineStr">
@@ -14018,7 +14018,7 @@
     <row r="117" ht="15" customHeight="1" s="66">
       <c r="A117" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025116</t>
+          <t>CAMP-2026116</t>
         </is>
       </c>
       <c r="B117" s="102" t="inlineStr">
@@ -14108,7 +14108,7 @@
     <row r="118" ht="15" customHeight="1" s="66">
       <c r="A118" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025117</t>
+          <t>CAMP-2026117</t>
         </is>
       </c>
       <c r="B118" s="94" t="inlineStr">
@@ -14198,7 +14198,7 @@
     <row r="119" ht="15" customHeight="1" s="66">
       <c r="A119" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025118</t>
+          <t>CAMP-2026118</t>
         </is>
       </c>
       <c r="B119" s="102" t="inlineStr">
@@ -14288,7 +14288,7 @@
     <row r="120" ht="15" customHeight="1" s="66">
       <c r="A120" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025119</t>
+          <t>CAMP-2026119</t>
         </is>
       </c>
       <c r="B120" s="94" t="inlineStr">
@@ -14378,7 +14378,7 @@
     <row r="121" ht="15" customHeight="1" s="66">
       <c r="A121" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025120</t>
+          <t>CAMP-2026120</t>
         </is>
       </c>
       <c r="B121" s="102" t="inlineStr">
@@ -14468,7 +14468,7 @@
     <row r="122" ht="15" customHeight="1" s="66">
       <c r="A122" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025121</t>
+          <t>CAMP-2026121</t>
         </is>
       </c>
       <c r="B122" s="94" t="inlineStr">
@@ -14558,7 +14558,7 @@
     <row r="123" ht="15" customHeight="1" s="66">
       <c r="A123" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025122</t>
+          <t>CAMP-2026122</t>
         </is>
       </c>
       <c r="B123" s="102" t="inlineStr">
@@ -14648,7 +14648,7 @@
     <row r="124" ht="15" customHeight="1" s="66">
       <c r="A124" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025123</t>
+          <t>CAMP-2026123</t>
         </is>
       </c>
       <c r="B124" s="94" t="inlineStr">
@@ -14738,7 +14738,7 @@
     <row r="125" ht="15" customHeight="1" s="66">
       <c r="A125" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025124</t>
+          <t>CAMP-2026124</t>
         </is>
       </c>
       <c r="B125" s="102" t="inlineStr">
@@ -14828,7 +14828,7 @@
     <row r="126" ht="15" customHeight="1" s="66">
       <c r="A126" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025125</t>
+          <t>CAMP-2026125</t>
         </is>
       </c>
       <c r="B126" s="94" t="inlineStr">
@@ -14918,7 +14918,7 @@
     <row r="127" ht="15" customHeight="1" s="66">
       <c r="A127" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025126</t>
+          <t>CAMP-2026126</t>
         </is>
       </c>
       <c r="B127" s="102" t="inlineStr">
@@ -15008,7 +15008,7 @@
     <row r="128" ht="15" customHeight="1" s="66">
       <c r="A128" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025127</t>
+          <t>CAMP-2026127</t>
         </is>
       </c>
       <c r="B128" s="94" t="inlineStr">
@@ -15098,7 +15098,7 @@
     <row r="129" ht="15" customHeight="1" s="66">
       <c r="A129" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025128</t>
+          <t>CAMP-2026128</t>
         </is>
       </c>
       <c r="B129" s="102" t="inlineStr">
@@ -15188,7 +15188,7 @@
     <row r="130" ht="15" customHeight="1" s="66">
       <c r="A130" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025129</t>
+          <t>CAMP-2026129</t>
         </is>
       </c>
       <c r="B130" s="94" t="inlineStr">
@@ -15278,7 +15278,7 @@
     <row r="131" ht="15" customHeight="1" s="66">
       <c r="A131" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025130</t>
+          <t>CAMP-2026130</t>
         </is>
       </c>
       <c r="B131" s="102" t="inlineStr">
@@ -15368,7 +15368,7 @@
     <row r="132" ht="15" customHeight="1" s="66">
       <c r="A132" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025131</t>
+          <t>CAMP-2026131</t>
         </is>
       </c>
       <c r="B132" s="94" t="inlineStr">
@@ -15458,7 +15458,7 @@
     <row r="133" ht="15" customHeight="1" s="66">
       <c r="A133" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025132</t>
+          <t>CAMP-2026132</t>
         </is>
       </c>
       <c r="B133" s="102" t="inlineStr">
@@ -15548,7 +15548,7 @@
     <row r="134" ht="15" customHeight="1" s="66">
       <c r="A134" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025133</t>
+          <t>CAMP-2026133</t>
         </is>
       </c>
       <c r="B134" s="94" t="inlineStr">
@@ -15638,7 +15638,7 @@
     <row r="135" ht="15" customHeight="1" s="66">
       <c r="A135" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025134</t>
+          <t>CAMP-2026134</t>
         </is>
       </c>
       <c r="B135" s="102" t="inlineStr">
@@ -15728,7 +15728,7 @@
     <row r="136" ht="15" customHeight="1" s="66">
       <c r="A136" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025135</t>
+          <t>CAMP-2026135</t>
         </is>
       </c>
       <c r="B136" s="94" t="inlineStr">
@@ -15818,7 +15818,7 @@
     <row r="137" ht="15" customHeight="1" s="66">
       <c r="A137" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025136</t>
+          <t>CAMP-2026136</t>
         </is>
       </c>
       <c r="B137" s="102" t="inlineStr">
@@ -15908,7 +15908,7 @@
     <row r="138" ht="15" customHeight="1" s="66">
       <c r="A138" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025137</t>
+          <t>CAMP-2026137</t>
         </is>
       </c>
       <c r="B138" s="94" t="inlineStr">
@@ -15998,7 +15998,7 @@
     <row r="139" ht="15" customHeight="1" s="66">
       <c r="A139" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025138</t>
+          <t>CAMP-2026138</t>
         </is>
       </c>
       <c r="B139" s="102" t="inlineStr">
@@ -16088,7 +16088,7 @@
     <row r="140" ht="15" customHeight="1" s="66">
       <c r="A140" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025139</t>
+          <t>CAMP-2026139</t>
         </is>
       </c>
       <c r="B140" s="94" t="inlineStr">
@@ -16178,7 +16178,7 @@
     <row r="141" ht="15" customHeight="1" s="66">
       <c r="A141" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025140</t>
+          <t>CAMP-2026140</t>
         </is>
       </c>
       <c r="B141" s="102" t="inlineStr">
@@ -16268,7 +16268,7 @@
     <row r="142" ht="15" customHeight="1" s="66">
       <c r="A142" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025141</t>
+          <t>CAMP-2026141</t>
         </is>
       </c>
       <c r="B142" s="94" t="inlineStr">
@@ -16358,7 +16358,7 @@
     <row r="143" ht="15" customHeight="1" s="66">
       <c r="A143" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025142</t>
+          <t>CAMP-2026142</t>
         </is>
       </c>
       <c r="B143" s="102" t="inlineStr">
@@ -16448,7 +16448,7 @@
     <row r="144" ht="15" customHeight="1" s="66">
       <c r="A144" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025143</t>
+          <t>CAMP-2026143</t>
         </is>
       </c>
       <c r="B144" s="94" t="inlineStr">
@@ -16538,7 +16538,7 @@
     <row r="145" ht="15" customHeight="1" s="66">
       <c r="A145" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025144</t>
+          <t>CAMP-2026144</t>
         </is>
       </c>
       <c r="B145" s="102" t="inlineStr">
@@ -16628,7 +16628,7 @@
     <row r="146" ht="15" customHeight="1" s="66">
       <c r="A146" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025145</t>
+          <t>CAMP-2026145</t>
         </is>
       </c>
       <c r="B146" s="94" t="inlineStr">
@@ -16718,7 +16718,7 @@
     <row r="147" ht="15" customHeight="1" s="66">
       <c r="A147" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025146</t>
+          <t>CAMP-2026146</t>
         </is>
       </c>
       <c r="B147" s="102" t="inlineStr">
@@ -16808,7 +16808,7 @@
     <row r="148" ht="15" customHeight="1" s="66">
       <c r="A148" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025147</t>
+          <t>CAMP-2026147</t>
         </is>
       </c>
       <c r="B148" s="94" t="inlineStr">
@@ -16898,7 +16898,7 @@
     <row r="149" ht="15" customHeight="1" s="66">
       <c r="A149" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025148</t>
+          <t>CAMP-2026148</t>
         </is>
       </c>
       <c r="B149" s="102" t="inlineStr">
@@ -16988,7 +16988,7 @@
     <row r="150" ht="15" customHeight="1" s="66">
       <c r="A150" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025149</t>
+          <t>CAMP-2026149</t>
         </is>
       </c>
       <c r="B150" s="94" t="inlineStr">
@@ -17078,7 +17078,7 @@
     <row r="151" ht="15" customHeight="1" s="66">
       <c r="A151" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025150</t>
+          <t>CAMP-2026150</t>
         </is>
       </c>
       <c r="B151" s="102" t="inlineStr">
@@ -17168,7 +17168,7 @@
     <row r="152" ht="15" customHeight="1" s="66">
       <c r="A152" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025151</t>
+          <t>CAMP-2026151</t>
         </is>
       </c>
       <c r="B152" s="94" t="inlineStr">
@@ -17258,7 +17258,7 @@
     <row r="153" ht="15" customHeight="1" s="66">
       <c r="A153" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025152</t>
+          <t>CAMP-2026152</t>
         </is>
       </c>
       <c r="B153" s="102" t="inlineStr">
@@ -17348,7 +17348,7 @@
     <row r="154" ht="15" customHeight="1" s="66">
       <c r="A154" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025153</t>
+          <t>CAMP-2026153</t>
         </is>
       </c>
       <c r="B154" s="94" t="inlineStr">
@@ -17438,7 +17438,7 @@
     <row r="155" ht="15" customHeight="1" s="66">
       <c r="A155" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025154</t>
+          <t>CAMP-2026154</t>
         </is>
       </c>
       <c r="B155" s="102" t="inlineStr">
@@ -17528,7 +17528,7 @@
     <row r="156" ht="15" customHeight="1" s="66">
       <c r="A156" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025155</t>
+          <t>CAMP-2026155</t>
         </is>
       </c>
       <c r="B156" s="94" t="inlineStr">
@@ -17618,7 +17618,7 @@
     <row r="157" ht="15" customHeight="1" s="66">
       <c r="A157" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025156</t>
+          <t>CAMP-2026156</t>
         </is>
       </c>
       <c r="B157" s="102" t="inlineStr">
@@ -17708,7 +17708,7 @@
     <row r="158" ht="15" customHeight="1" s="66">
       <c r="A158" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025157</t>
+          <t>CAMP-2026157</t>
         </is>
       </c>
       <c r="B158" s="94" t="inlineStr">
@@ -17798,7 +17798,7 @@
     <row r="159" ht="15" customHeight="1" s="66">
       <c r="A159" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025158</t>
+          <t>CAMP-2026158</t>
         </is>
       </c>
       <c r="B159" s="102" t="inlineStr">
@@ -17888,7 +17888,7 @@
     <row r="160" ht="15" customHeight="1" s="66">
       <c r="A160" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025159</t>
+          <t>CAMP-2026159</t>
         </is>
       </c>
       <c r="B160" s="94" t="inlineStr">
@@ -17978,7 +17978,7 @@
     <row r="161" ht="15" customHeight="1" s="66">
       <c r="A161" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025160</t>
+          <t>CAMP-2026160</t>
         </is>
       </c>
       <c r="B161" s="102" t="inlineStr">
@@ -18068,7 +18068,7 @@
     <row r="162" ht="15" customHeight="1" s="66">
       <c r="A162" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025161</t>
+          <t>CAMP-2026161</t>
         </is>
       </c>
       <c r="B162" s="94" t="inlineStr">
@@ -18158,7 +18158,7 @@
     <row r="163" ht="15" customHeight="1" s="66">
       <c r="A163" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025162</t>
+          <t>CAMP-2026162</t>
         </is>
       </c>
       <c r="B163" s="102" t="inlineStr">
@@ -18248,7 +18248,7 @@
     <row r="164" ht="15" customHeight="1" s="66">
       <c r="A164" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025163</t>
+          <t>CAMP-2026163</t>
         </is>
       </c>
       <c r="B164" s="94" t="inlineStr">
@@ -18338,7 +18338,7 @@
     <row r="165" ht="15" customHeight="1" s="66">
       <c r="A165" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025164</t>
+          <t>CAMP-2026164</t>
         </is>
       </c>
       <c r="B165" s="102" t="inlineStr">
@@ -18428,7 +18428,7 @@
     <row r="166" ht="15" customHeight="1" s="66">
       <c r="A166" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025165</t>
+          <t>CAMP-2026165</t>
         </is>
       </c>
       <c r="B166" s="94" t="inlineStr">
@@ -18518,7 +18518,7 @@
     <row r="167" ht="15" customHeight="1" s="66">
       <c r="A167" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025166</t>
+          <t>CAMP-2026166</t>
         </is>
       </c>
       <c r="B167" s="102" t="inlineStr">
@@ -18608,7 +18608,7 @@
     <row r="168" ht="15" customHeight="1" s="66">
       <c r="A168" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025167</t>
+          <t>CAMP-2026167</t>
         </is>
       </c>
       <c r="B168" s="94" t="inlineStr">
@@ -18698,7 +18698,7 @@
     <row r="169" ht="15" customHeight="1" s="66">
       <c r="A169" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025168</t>
+          <t>CAMP-2026168</t>
         </is>
       </c>
       <c r="B169" s="102" t="inlineStr">
@@ -18788,7 +18788,7 @@
     <row r="170" ht="15" customHeight="1" s="66">
       <c r="A170" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025169</t>
+          <t>CAMP-2026169</t>
         </is>
       </c>
       <c r="B170" s="94" t="inlineStr">
@@ -18878,7 +18878,7 @@
     <row r="171" ht="15" customHeight="1" s="66">
       <c r="A171" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025170</t>
+          <t>CAMP-2026170</t>
         </is>
       </c>
       <c r="B171" s="102" t="inlineStr">
@@ -18968,7 +18968,7 @@
     <row r="172" ht="15" customHeight="1" s="66">
       <c r="A172" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025171</t>
+          <t>CAMP-2026171</t>
         </is>
       </c>
       <c r="B172" s="94" t="inlineStr">
@@ -19058,7 +19058,7 @@
     <row r="173" ht="15" customHeight="1" s="66">
       <c r="A173" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025172</t>
+          <t>CAMP-2026172</t>
         </is>
       </c>
       <c r="B173" s="102" t="inlineStr">
@@ -19148,7 +19148,7 @@
     <row r="174" ht="15" customHeight="1" s="66">
       <c r="A174" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025173</t>
+          <t>CAMP-2026173</t>
         </is>
       </c>
       <c r="B174" s="94" t="inlineStr">
@@ -19238,7 +19238,7 @@
     <row r="175" ht="15" customHeight="1" s="66">
       <c r="A175" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025174</t>
+          <t>CAMP-2026174</t>
         </is>
       </c>
       <c r="B175" s="102" t="inlineStr">
@@ -19328,7 +19328,7 @@
     <row r="176" ht="15" customHeight="1" s="66">
       <c r="A176" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025175</t>
+          <t>CAMP-2026175</t>
         </is>
       </c>
       <c r="B176" s="94" t="inlineStr">
@@ -19418,7 +19418,7 @@
     <row r="177" ht="15" customHeight="1" s="66">
       <c r="A177" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025176</t>
+          <t>CAMP-2026176</t>
         </is>
       </c>
       <c r="B177" s="102" t="inlineStr">
@@ -19508,7 +19508,7 @@
     <row r="178" ht="15" customHeight="1" s="66">
       <c r="A178" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025177</t>
+          <t>CAMP-2026177</t>
         </is>
       </c>
       <c r="B178" s="94" t="inlineStr">
@@ -19598,7 +19598,7 @@
     <row r="179" ht="15" customHeight="1" s="66">
       <c r="A179" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025178</t>
+          <t>CAMP-2026178</t>
         </is>
       </c>
       <c r="B179" s="102" t="inlineStr">
@@ -19688,7 +19688,7 @@
     <row r="180" ht="15" customHeight="1" s="66">
       <c r="A180" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025179</t>
+          <t>CAMP-2026179</t>
         </is>
       </c>
       <c r="B180" s="94" t="inlineStr">
@@ -19778,7 +19778,7 @@
     <row r="181" ht="15" customHeight="1" s="66">
       <c r="A181" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025180</t>
+          <t>CAMP-2026180</t>
         </is>
       </c>
       <c r="B181" s="102" t="inlineStr">
@@ -19868,7 +19868,7 @@
     <row r="182" ht="15" customHeight="1" s="66">
       <c r="A182" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025181</t>
+          <t>CAMP-2026181</t>
         </is>
       </c>
       <c r="B182" s="94" t="inlineStr">
@@ -19958,7 +19958,7 @@
     <row r="183" ht="15" customHeight="1" s="66">
       <c r="A183" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025182</t>
+          <t>CAMP-2026182</t>
         </is>
       </c>
       <c r="B183" s="102" t="inlineStr">
@@ -20048,7 +20048,7 @@
     <row r="184" ht="15" customHeight="1" s="66">
       <c r="A184" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025183</t>
+          <t>CAMP-2026183</t>
         </is>
       </c>
       <c r="B184" s="94" t="inlineStr">
@@ -20138,7 +20138,7 @@
     <row r="185" ht="15" customHeight="1" s="66">
       <c r="A185" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025184</t>
+          <t>CAMP-2026184</t>
         </is>
       </c>
       <c r="B185" s="102" t="inlineStr">
@@ -20228,7 +20228,7 @@
     <row r="186" ht="15" customHeight="1" s="66">
       <c r="A186" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025185</t>
+          <t>CAMP-2026185</t>
         </is>
       </c>
       <c r="B186" s="94" t="inlineStr">
@@ -20318,7 +20318,7 @@
     <row r="187" ht="15" customHeight="1" s="66">
       <c r="A187" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025186</t>
+          <t>CAMP-2026186</t>
         </is>
       </c>
       <c r="B187" s="102" t="inlineStr">
@@ -20408,7 +20408,7 @@
     <row r="188" ht="15" customHeight="1" s="66">
       <c r="A188" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025187</t>
+          <t>CAMP-2026187</t>
         </is>
       </c>
       <c r="B188" s="94" t="inlineStr">
@@ -20498,7 +20498,7 @@
     <row r="189" ht="15" customHeight="1" s="66">
       <c r="A189" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025188</t>
+          <t>CAMP-2026188</t>
         </is>
       </c>
       <c r="B189" s="102" t="inlineStr">
@@ -20588,7 +20588,7 @@
     <row r="190" ht="15" customHeight="1" s="66">
       <c r="A190" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025189</t>
+          <t>CAMP-2026189</t>
         </is>
       </c>
       <c r="B190" s="94" t="inlineStr">
@@ -20678,7 +20678,7 @@
     <row r="191" ht="15" customHeight="1" s="66">
       <c r="A191" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025190</t>
+          <t>CAMP-2026190</t>
         </is>
       </c>
       <c r="B191" s="102" t="inlineStr">
@@ -20768,7 +20768,7 @@
     <row r="192" ht="15" customHeight="1" s="66">
       <c r="A192" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025191</t>
+          <t>CAMP-2026191</t>
         </is>
       </c>
       <c r="B192" s="94" t="inlineStr">
@@ -20858,7 +20858,7 @@
     <row r="193" ht="15" customHeight="1" s="66">
       <c r="A193" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025192</t>
+          <t>CAMP-2026192</t>
         </is>
       </c>
       <c r="B193" s="102" t="inlineStr">
@@ -20948,7 +20948,7 @@
     <row r="194" ht="15" customHeight="1" s="66">
       <c r="A194" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025193</t>
+          <t>CAMP-2026193</t>
         </is>
       </c>
       <c r="B194" s="94" t="inlineStr">
@@ -21038,7 +21038,7 @@
     <row r="195" ht="15" customHeight="1" s="66">
       <c r="A195" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025194</t>
+          <t>CAMP-2026194</t>
         </is>
       </c>
       <c r="B195" s="102" t="inlineStr">
@@ -21128,7 +21128,7 @@
     <row r="196" ht="15" customHeight="1" s="66">
       <c r="A196" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025195</t>
+          <t>CAMP-2026195</t>
         </is>
       </c>
       <c r="B196" s="94" t="inlineStr">
@@ -21218,7 +21218,7 @@
     <row r="197" ht="15" customHeight="1" s="66">
       <c r="A197" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025196</t>
+          <t>CAMP-2026196</t>
         </is>
       </c>
       <c r="B197" s="102" t="inlineStr">
@@ -21308,7 +21308,7 @@
     <row r="198" ht="15" customHeight="1" s="66">
       <c r="A198" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025197</t>
+          <t>CAMP-2026197</t>
         </is>
       </c>
       <c r="B198" s="94" t="inlineStr">
@@ -21398,7 +21398,7 @@
     <row r="199" ht="15" customHeight="1" s="66">
       <c r="A199" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025198</t>
+          <t>CAMP-2026198</t>
         </is>
       </c>
       <c r="B199" s="102" t="inlineStr">
@@ -21488,7 +21488,7 @@
     <row r="200" ht="15" customHeight="1" s="66">
       <c r="A200" s="94" t="inlineStr">
         <is>
-          <t>CAMP-2025199</t>
+          <t>CAMP-2026199</t>
         </is>
       </c>
       <c r="B200" s="94" t="inlineStr">
@@ -21578,7 +21578,7 @@
     <row r="201" ht="15" customHeight="1" s="66">
       <c r="A201" s="102" t="inlineStr">
         <is>
-          <t>CAMP-2025200</t>
+          <t>CAMP-2026200</t>
         </is>
       </c>
       <c r="B201" s="102" t="inlineStr">
@@ -25363,6 +25363,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="66">
       <c r="A3" s="125" t="inlineStr">
         <is>
